--- a/MA_Pipeline_Populated.xlsx
+++ b/MA_Pipeline_Populated.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Pipeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Disqualified — PE Backed" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Research Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Disqualified" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Email Cheatsheet" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pipeline'!$A$1:$V$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pipeline'!$A$1:$V$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,7 +48,8 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001155CC"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
       <sz val="10"/>
       <u val="single"/>
     </font>
@@ -65,6 +66,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="001155CC"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="007F6000"/>
       <sz val="10"/>
     </font>
@@ -76,13 +83,24 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="00843C0C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00595959"/>
-      <sz val="9"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -90,35 +108,8 @@
       <color rgb="00375623"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00375623"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="007F6000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="007F6000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00843C0C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00843C0C"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -152,6 +143,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00595959"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00843C0C"/>
       </patternFill>
     </fill>
@@ -162,7 +163,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00D6E4F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -192,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -221,59 +222,77 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -640,11 +659,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -658,13 +677,13 @@
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="38" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="44" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="46" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -779,60 +798,60 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="72" customHeight="1">
+    <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Russell Reid Waste Management</t>
+          <t>Aiello Home Services</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>russellreid.com</t>
+          <t>aiellohomeservices.com</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Windsor Locks</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Waste Management / Environmental</t>
+          <t>HVAC / Plumbing / Electrical</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>$30M–$60M</t>
+          <t>$22M</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>$5M–$10M</t>
+          <t>$3M–$4M</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>100–200</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Family-owned (2nd gen)</t>
+          <t>Family (4th gen)</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>~1935</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Yes (5 locations)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -847,95 +866,95 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Gary M. Weiner</t>
+          <t>Michael Jezouit</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>President &amp; CEO</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>gweiner@russellreid.com</t>
+          <t>m.jezouit@aiellohomeservices.com ✓</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>(800) 356-4468</t>
+          <t>(860) 292-2600</t>
         </is>
       </c>
       <c r="R2" s="7" t="inlineStr">
         <is>
-          <t>linkedin.com/company/russellreidresponsiblewastemanagement</t>
+          <t>linkedin.com/in/michael-jezouit-0b18a0126/</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>Verify email; call main line to confirm Gary Weiner is decision-maker; send intro letter</t>
+          <t>SEND NOW — email confirmed. Reference 90-yr legacy + succession planning.</t>
         </is>
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
-          <t>80+ year family business, 5 NJ/NY/PA/DE locations, septic &amp; grease trap pumping. Morton Weiner (founder) acquired 1981; son Gary now runs it. Classic boomer transition setup. Waste services = recurring revenue + limited substitutes = PE loves this.</t>
+          <t>4th-gen family, 90+ years, $22M rev, 60 employees, CT market. Michael Jezouit as non-family CEO = owners (Aiello family) may be open to exit. EMAIL CONFIRMED via ZoomInfo + RocketReach.</t>
         </is>
       </c>
       <c r="V2" s="9" t="inlineStr">
         <is>
-          <t>Confirm email format; confirm no PE involvement; verify Gary is ready to discuss exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="72" customHeight="1">
+          <t>Confirm Aiello family still owns (not Jezouit); confirm no PE; check if LOI outstanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Aiello Home Services</t>
+          <t>Princeton Air Conditioning</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>aiellohomeservices.com</t>
+          <t>princetonair.com</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Windsor Locks</t>
+          <t>Princeton Junction</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>HVAC / Plumbing / Electrical</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>$22M</t>
+          <t>$10M–$20M</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>$3M–$4M</t>
+          <t>$1.5M–$3M</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40–75</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Family-owned (4th gen)</t>
+          <t>Family (2nd gen, founder died Oct 2024)</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>~1935</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -955,371 +974,371 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Michael Jezouit</t>
+          <t>J. Scott Needham</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>President &amp; CEO</t>
-        </is>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>m.jezouit@aiellohomeservices.com</t>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>s.needham@princetonair.com</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>(860) 292-2600</t>
+          <t>(877) 947-9090</t>
         </is>
       </c>
       <c r="R3" s="7" t="inlineStr">
         <is>
-          <t>linkedin.com/in/michael-jezouit-0b18a0126/</t>
+          <t>linkedin.com/in/j-scott-needham-90061211/</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>Send personalized email referencing 90-year family legacy; mention succession planning angle</t>
+          <t>HOT — founder Joe Needham died Oct 2024. Scott just inherited. Reach out with empathy + succession conversation NOW.</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
         <is>
-          <t>4th-generation family business, 90+ years. $22M revenue, 60 employees, CT market. Home services = fragmented market, PE loves roll-ups. Michael Jezouit as non-family CEO suggests owners may be open to transition. EMAIL CONFIRMED via multiple data sources (m.jezouit@aiellohomeservices.com).</t>
+          <t>SUCCESSION EVENT: Founder Joe Needham (91) died Oct 2024. Son Scott Needham now president. Classic forced transition moment — often the best time to start M&amp;A conversation. 50+ year Central NJ HVAC. Email at s.needham@princetonair.com (ZoomInfo shows s***@princetonair.com).</t>
         </is>
       </c>
       <c r="V3" s="9" t="inlineStr">
         <is>
-          <t>Confirm owners are Aiello family (not Jezouit); confirm no recent PE investment; check if any LOI outstanding</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="72" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Confires Fire Protection</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>confires.com</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
+          <t>Confirm Scott is sole decision-maker; confirm no PE approach; verify rev range</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Fireline Corporation</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>fireline.com</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Baltimore</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Fire Protection / Life Safety</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>$25M–$40M</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>$4M–$6M</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>100–175</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Family (3rd gen)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Yes (MD + PA)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Anna Waters Gavin</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>agavin@fireline.com ✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>(410) 247-1422</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/annaatfireline</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>SEND NOW — email confirmed. 75-yr institution, 3rd gen, perfect PE target. Pitch confidential process.</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>75-year-old Baltimore fire protection company. John Waters founded 1947 → son Stephen → daughter Anna Waters Gavin (3rd gen). EMAIL CONFIRMED: agavin@fireline.com. $25-40M revenue, fire inspection + service = recurring government-mandated revenue. Top-tier PE roll-up candidate.</t>
+        </is>
+      </c>
+      <c r="V4" s="9" t="inlineStr">
+        <is>
+          <t>Confirm no current sale process; verify EBITDA margin; check if any PE approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Bruni &amp; Campisi</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>bruniandcampisi.com</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Elmsford</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>HVAC / Plumbing</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>$29.9M</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>$4M–$6M</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>60–85</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Family (2nd gen)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Keith Bruni</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>k.bruni@bruniandcampisi.com</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>(914) 214-1550</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/keith-bruni-6082b055/</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>Email + LinkedIn. ~$30M revenue Westchester — mention platform potential.</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>~$30M rev, Westchester NY, 45 years. HVAC+plumbing combo = high-ticket recurring contracts. Keith Bruni (2nd gen President); founders Mario Bruni and Frank Campisi are likely retirement age. Strong PE roll-up candidate in high-income market.</t>
+        </is>
+      </c>
+      <c r="V5" s="9" t="inlineStr">
+        <is>
+          <t>Confirm founders' current roles; confirm email format; check comp landscape</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Mazza Recycling Services</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>mazzarecycling.com</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>NJ</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>South Plainfield</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Fire Protection / Life Safety</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>$5M–$10M</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>$750K–$1.5M</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>Privately held</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>~1985</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>Yes (affiliated offices)</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Tinton Falls</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Recycling / Waste Management</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>$25M–$40M</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>$3M–$5M</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>100–175</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Family (2nd gen)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Researching</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>William Wrublevski</t>
-        </is>
-      </c>
-      <c r="O4" s="10" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="P4" s="14" t="inlineStr">
-        <is>
-          <t>william.wrublevski@confires.com</t>
-        </is>
-      </c>
-      <c r="Q4" s="11" t="inlineStr">
-        <is>
-          <t>(888) 228-0917</t>
-        </is>
-      </c>
-      <c r="R4" s="15" t="inlineStr">
-        <is>
-          <t>linkedin.com/company/confires-fire-protection-services-llc/</t>
-        </is>
-      </c>
-      <c r="S4" s="11" t="inlineStr"/>
-      <c r="T4" s="16" t="inlineStr">
-        <is>
-          <t>Verify William Wrublevski is still active owner; also cc VP Mark Calleo (mark.calleo@confires.com)</t>
-        </is>
-      </c>
-      <c r="U4" s="16" t="inlineStr">
-        <is>
-          <t>40+ years serving NJ/DE/PA. Fire protection is a recurring-revenue inspection/service business — extremely attractive to PE. Owner William Wrublevski likely retirement-age. Email format: first.last@confires.com confirmed via RocketReach.</t>
-        </is>
-      </c>
-      <c r="V4" s="17" t="inlineStr">
-        <is>
-          <t>Confirm W. Wrublevski ownership stake; confirm email; check if part of any roll-up already</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="72" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>T.F. O'Brien &amp; Co.</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>tfobrien.com</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>New Hyde Park</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>HVAC / Cooling &amp; Heating</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>$10M–$20M</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>$1.5M–$3M</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>25–35</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>Family-owned (3rd gen)</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>1934</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
-      <c r="N5" s="10" t="inlineStr">
-        <is>
-          <t>Kerry O'Brien</t>
-        </is>
-      </c>
-      <c r="O5" s="10" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="P5" s="14" t="inlineStr">
-        <is>
-          <t>k.obrien@tfobrien.com</t>
-        </is>
-      </c>
-      <c r="Q5" s="11" t="inlineStr">
-        <is>
-          <t>(516) 488-1800</t>
-        </is>
-      </c>
-      <c r="R5" s="15" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/kerry-o-brien-b7906b6/</t>
-        </is>
-      </c>
-      <c r="S5" s="11" t="inlineStr"/>
-      <c r="T5" s="16" t="inlineStr">
-        <is>
-          <t>Reach out via LinkedIn + email; acknowledge 90+ year legacy; pitch confidential process</t>
-        </is>
-      </c>
-      <c r="U5" s="16" t="inlineStr">
-        <is>
-          <t>90+ year Long Island HVAC institution. 3rd-gen family ownership (Kerry, Thomas Jr., Christopher O'Brien). Classic succession play — multiple heirs often means disagreement on direction, creating exit motivation. Strong brand in high-income Long Island market.</t>
-        </is>
-      </c>
-      <c r="V5" s="17" t="inlineStr">
-        <is>
-          <t>Confirm current co-owner names; confirm revenue; check if any PE approached them before</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Bruni &amp; Campisi</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>bruniandcampisi.com</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Elmsford</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>HVAC / Plumbing</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>$29.9M</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>$4M–$6M</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>60–85</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Family-owned (2nd gen)</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Keith Bruni</t>
+          <t>James Mazza Jr.</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>k.bruni@bruniandcampisi.com</t>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>j.mazza@mazzarecycling.com</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>(914) 214-1550</t>
+          <t>(732) 992-8055</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>linkedin.com/in/keith-bruni-6082b055/</t>
+          <t>linkedin.com/in/james-mazza-7614b316b/</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>Send email + LinkedIn connection; reference Westchester market strength and platform potential</t>
+          <t>Email + LinkedIn. Central NJ recycler. Reference ESG and PE appetite for recycling.</t>
         </is>
       </c>
       <c r="U6" s="8" t="inlineStr">
         <is>
-          <t>~$30M revenue, Westchester NY, 45+ years. HVAC+plumbing combo = higher ticket, recurring maintenance contracts. Keith Bruni (president) is 2nd gen; founders Mario Bruni and Frank Campisi are likely retirement age. Strong PE roll-up candidate.</t>
+          <t>60-year-old family recycling company. Dominick and James Mazza Sr. founded 1964; James Jr. now runs it. $25-40M revenue. Central NJ recycling + C&amp;D waste — PE loves recurring, route-based environmental services. Recently acquired Liberty Waste (2024), showing growth appetite.</t>
         </is>
       </c>
       <c r="V6" s="9" t="inlineStr">
         <is>
-          <t>Confirm founders' current roles; confirm email format; check Westchester competitor landscape</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="72" customHeight="1">
+          <t>Confirm no PE involvement; check post-Liberty acquisition financials; verify email format</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Mowrey Elevator</t>
@@ -1362,7 +1381,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Family-owned (founder-led)</t>
+          <t>Family (founder-led)</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1395,7 +1414,7 @@
           <t>Founder &amp; President</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr">
+      <c r="P7" s="10" t="inlineStr">
         <is>
           <t>t.mowrey@mowreyelevator.com</t>
         </is>
@@ -1413,22 +1432,994 @@
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>Call + email Tim directly; elevator service is a niche PE loves — mention specific elevator roll-up comps</t>
+          <t>Call + email Tim directly. Reference elevator roll-up activity (Arcline, Kone, etc).</t>
         </is>
       </c>
       <c r="U7" s="8" t="inlineStr">
         <is>
-          <t>50-year-old founder-led elevator company, $19.5M revenue, 50-75 employees, FL. Elevator service = govt-regulated, recurring maintenance contracts, very high switching costs. Mowrey branded as 'The Elevator Man' — strong regional reputation. Classic niche boomer business.</t>
+          <t>50-year founder-led elevator company, $19.5M rev, FL. Elevator service = govt-regulated recurring maintenance, very high switching costs. 'The Elevator Man' brand = strong regional presence. Classic niche boomer business — Tim Sr. likely approaching exit.</t>
         </is>
       </c>
       <c r="V7" s="9" t="inlineStr">
         <is>
-          <t>Confirm Tim Sr. is still primary decision-maker vs. Tim Jr.; confirm no PE approach; verify email</t>
+          <t>Confirm Tim Sr. vs Tim Jr. as decision-maker; verify email; confirm no PE approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Russell Reid Waste Management</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>russellreid.com</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Edison</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Septic / Liquid Waste</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>$30M–$60M</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>$5M–$10M</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>100–200</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Family (2nd gen)</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>1943</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Yes (5 locations)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Gary M. Weiner</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>gweiner@russellreid.com</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>(800) 356-4468</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/russellreidresponsiblewastemanagement</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>Verify Gary Weiner email; call main line. NJ's largest independent liquid waster.</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>80-year family business, 5 NJ/NY/PA/DE locations. Morton Weiner acquired 1943 company in 1981; son Gary now President. Septic+grease trap = recurring, non-discretionary. Scale + geography = ideal PE platform. Largest independent liquid waste in NJ.</t>
+        </is>
+      </c>
+      <c r="V8" s="9" t="inlineStr">
+        <is>
+          <t>Confirm Gary Weiner email format; confirm no active sale process; verify revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Burkholder's HVAC</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>burkholders-hvac.com</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Emmaus</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>$8M–$15M</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>$1M–$2.5M</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>40–70</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>Family (2nd gen)</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>Robert (Bob) Burkholder</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P9" s="15" t="inlineStr">
+        <is>
+          <t>r.burkholder@burkholders-hvac.com</t>
+        </is>
+      </c>
+      <c r="Q9" s="12" t="inlineStr">
+        <is>
+          <t>(610) 816-6889</t>
+        </is>
+      </c>
+      <c r="R9" s="16" t="inlineStr">
+        <is>
+          <t>burkholders-hvac.com/our-team/</t>
+        </is>
+      </c>
+      <c r="S9" s="12" t="inlineStr"/>
+      <c r="T9" s="17" t="inlineStr">
+        <is>
+          <t>Call main line; confirm Bob's email. 65-year Lehigh Valley HVAC — strong succession signal.</t>
+        </is>
+      </c>
+      <c r="U9" s="17" t="inlineStr">
+        <is>
+          <t>Founded 1960 by Carl Burkholder; son Bob took over in 2000. 65+ years, Lehigh Valley PA. Carrier Factory Authorized Dealer = quality brand. Recently acquired Lande Heating (Bethlehem) — growth appetite. Bob is likely looking toward an exit in the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="V9" s="18" t="inlineStr">
+        <is>
+          <t>Confirm Bob's email (try bob@burkholders-hvac.com); confirm size; check if any PE approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Confires Fire Protection</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>confires.com</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>South Plainfield</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Fire Protection / Life Safety</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>$5M–$10M</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>$750K–$1.5M</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>Privately held</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>~1985</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>Yes (affiliated offices)</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>William Wrublevski</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P10" s="15" t="inlineStr">
+        <is>
+          <t>william.wrublevski@confires.com</t>
+        </is>
+      </c>
+      <c r="Q10" s="12" t="inlineStr">
+        <is>
+          <t>(888) 228-0917</t>
+        </is>
+      </c>
+      <c r="R10" s="16" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/confires-fire-protection-services-llc/</t>
+        </is>
+      </c>
+      <c r="S10" s="12" t="inlineStr"/>
+      <c r="T10" s="17" t="inlineStr">
+        <is>
+          <t>Verify Wrublevski still active owner; cc VP Mark Calleo (mark.calleo@confires.com)</t>
+        </is>
+      </c>
+      <c r="U10" s="17" t="inlineStr">
+        <is>
+          <t>40+ years NJ/DE/PA fire protection. Recurring inspection/service revenue. William Wrublevski (owner), Mark Calleo (VP). Email format first.last@confires.com CONFIRMED. Fire protection = PE's current favorite roll-up (Pye-Barker, Fortis dominating).</t>
+        </is>
+      </c>
+      <c r="V10" s="18" t="inlineStr">
+        <is>
+          <t>Confirm Wrublevski ownership stake; confirm still independent; check size</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>T.F. O'Brien &amp; Co.</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>tfobrien.com</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>New Hyde Park</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>HVAC / Cooling &amp; Heating</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>$10M–$18M</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>$1.5M–$2.5M</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>25–35</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>Family (3rd gen)</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>Kerry O'Brien</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P11" s="15" t="inlineStr">
+        <is>
+          <t>k.obrien@tfobrien.com</t>
+        </is>
+      </c>
+      <c r="Q11" s="12" t="inlineStr">
+        <is>
+          <t>(516) 488-1800</t>
+        </is>
+      </c>
+      <c r="R11" s="16" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/kerry-o-brien-b7906b6/</t>
+        </is>
+      </c>
+      <c r="S11" s="12" t="inlineStr"/>
+      <c r="T11" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn + email. 90+ yr Long Island HVAC. Multiple O'Brien siblings = succession complexity.</t>
+        </is>
+      </c>
+      <c r="U11" s="17" t="inlineStr">
+        <is>
+          <t>90+ year Long Island HVAC institution (1934). 3rd gen family (Kerry, Thomas Jr., Christopher O'Brien). Multiple heirs = succession complexity = exit motivation. Strong brand in high-income Long Island market.</t>
+        </is>
+      </c>
+      <c r="V11" s="18" t="inlineStr">
+        <is>
+          <t>Confirm current co-owner names; confirm revenue; verify email format</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Suburban Disposal</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>suburbandisposal.com</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Waste Management / Hauling</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>$17M</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>$2.5M–$4M</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>~100</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>John Roselle</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>Contact (verify title)</t>
+        </is>
+      </c>
+      <c r="P12" s="15" t="inlineStr">
+        <is>
+          <t>john.roselle@suburbandisposal.com</t>
+        </is>
+      </c>
+      <c r="Q12" s="12" t="inlineStr">
+        <is>
+          <t>(973) 227-7020</t>
+        </is>
+      </c>
+      <c r="R12" s="16" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/john-roselle-645399a0/</t>
+        </is>
+      </c>
+      <c r="S12" s="12" t="inlineStr"/>
+      <c r="T12" s="17" t="inlineStr">
+        <is>
+          <t>Call main line; find owner name. $17M Northern NJ hauler — decent size for add-on.</t>
+        </is>
+      </c>
+      <c r="U12" s="17" t="inlineStr">
+        <is>
+          <t>45-year Northern NJ waste hauler, $17M revenue, ~100 employees. Waste hauling = recurring, route-based, fragmented. Classic add-on for a regional platform acquirer. Fairfield NJ location is strategic.</t>
+        </is>
+      </c>
+      <c r="V12" s="18" t="inlineStr">
+        <is>
+          <t>Confirm who the owner is (John Roselle title unclear); confirm not PE-backed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>A Royal Flush</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>aroyalflush.com</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Bridgeport</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Portable Sanitation</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>$15M–$25M</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>$2M–$4M</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>75–125</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>Privately held</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>Yes (CT/NY/NJ/PA/MA/SC/FL)</t>
+        </is>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Tim Butler</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>Principal Owner &amp; Chairman</t>
+        </is>
+      </c>
+      <c r="P13" s="15" t="inlineStr">
+        <is>
+          <t>tbutler@aroyalflush.com</t>
+        </is>
+      </c>
+      <c r="Q13" s="12" t="inlineStr">
+        <is>
+          <t>(203) 333-1400</t>
+        </is>
+      </c>
+      <c r="R13" s="16" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/a-royal-flush-inc/</t>
+        </is>
+      </c>
+      <c r="S13" s="12" t="inlineStr"/>
+      <c r="T13" s="17" t="inlineStr">
+        <is>
+          <t>Email Tim Butler. 10,000+ unit fleet, 7-state footprint = platform-level portable sanitation.</t>
+        </is>
+      </c>
+      <c r="U13" s="17" t="inlineStr">
+        <is>
+          <t>30+ year CT portable sanitation leader. 10,000+ toilets, 80 trailers, 90 trucks. 7-state footprint (CT/NY/NJ/PA/MA/SC/FL) = true regional platform. Tim Butler took over after founder Bill Malone passed 2017. COO Mauro DaSilva. Portable sanitation = route-based, recurring, PE-loved.</t>
+        </is>
+      </c>
+      <c r="V13" s="18" t="inlineStr">
+        <is>
+          <t>Confirm Tim's email format; confirm ownership structure; check if any PE contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Texas Outhouse</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>texasouthouse.com</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Portable Sanitation</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>$10M–$20M</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>$1.5M–$3M</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>50–100</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>Family (Carl family)</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>Paul Carl</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P14" s="15" t="inlineStr">
+        <is>
+          <t>paul.carl@texasouthouse.com</t>
+        </is>
+      </c>
+      <c r="Q14" s="12" t="inlineStr">
+        <is>
+          <t>(713) 690-9800</t>
+        </is>
+      </c>
+      <c r="R14" s="16" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/texas-outhouse/</t>
+        </is>
+      </c>
+      <c r="S14" s="12" t="inlineStr"/>
+      <c r="T14" s="17" t="inlineStr">
+        <is>
+          <t>Email Paul Carl. Sister company Gainsborough Waste = potential double deal.</t>
+        </is>
+      </c>
+      <c r="U14" s="17" t="inlineStr">
+        <is>
+          <t>Houston metro portable sanitation leader. Carl family: W. Noble Carl III (father), Paul Carl (President/VP), Noble Jr. (brother). Also runs sister company Gainsborough Waste. Family-operated since 1999. Houston market = large construction base = strong recurring revenue.</t>
+        </is>
+      </c>
+      <c r="V14" s="18" t="inlineStr">
+        <is>
+          <t>Confirm Paul's email; confirm not PE-approached; check Gainsborough Waste ownership separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Revolution Recovery</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>revolutionrecovery.com</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Recycling / C&amp;D Waste</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>$20M–$35M</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>$3M–$5M</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>75–150</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>Founder-owned</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>Yes (Phila + Wilmington DE + Allentown PA)</t>
+        </is>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Jonathan Wybar</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>Founder &amp; Owner</t>
+        </is>
+      </c>
+      <c r="P15" s="15" t="inlineStr">
+        <is>
+          <t>jwybar@revolutionrecovery.com</t>
+        </is>
+      </c>
+      <c r="Q15" s="12" t="inlineStr">
+        <is>
+          <t>(215) 333-6505</t>
+        </is>
+      </c>
+      <c r="R15" s="16" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/revolution-recovery/</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr"/>
+      <c r="T15" s="17" t="inlineStr">
+        <is>
+          <t>Email Jonathan + call. C&amp;D recycling = strong PE interest. 3 locations = platform.</t>
+        </is>
+      </c>
+      <c r="U15" s="17" t="inlineStr">
+        <is>
+          <t>Philly-area C&amp;D recycler, 3 locations (PA + DE + Lehigh Valley), founded 2004 by Jonathan Wybar. Construction/demolition waste is fragmented and PE-active. Route-based + scale = acquisition target. 20 years old — Wybar may be thinking about liquidity.</t>
+        </is>
+      </c>
+      <c r="V15" s="18" t="inlineStr">
+        <is>
+          <t>Confirm Jonathan's email; confirm not PE-backed; verify revenue/employee count</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Bosworth Air Conditioning</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>bosworthac.com</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>$8M–$15M</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>$1M–$2M</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>40–70</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>Family (2nd gen)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M16" s="19" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N16" s="19" t="inlineStr">
+        <is>
+          <t>Jerry Bosworth Jr.</t>
+        </is>
+      </c>
+      <c r="O16" s="19" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>jerry@bosworthac.com</t>
+        </is>
+      </c>
+      <c r="Q16" s="20" t="inlineStr">
+        <is>
+          <t>(409) 762-0418</t>
+        </is>
+      </c>
+      <c r="R16" s="24" t="inlineStr">
+        <is>
+          <t>acca.org/board/jerry-bosworth/</t>
+        </is>
+      </c>
+      <c r="S16" s="20" t="inlineStr"/>
+      <c r="T16" s="25" t="inlineStr">
+        <is>
+          <t>Verify if Jerry Sr. or Jr. runs it now. 65+ year Gulf Coast HVAC.</t>
+        </is>
+      </c>
+      <c r="U16" s="25" t="inlineStr">
+        <is>
+          <t>65-year Galveston TX HVAC family business. Jerry Bosworth Sr. founded 1959; Jerry Jr. is current owner. Gulf Coast market = year-round AC demand. ACCA board member = industry credibility. Smaller size but solid family succession candidate.</t>
+        </is>
+      </c>
+      <c r="V16" s="26" t="inlineStr">
+        <is>
+          <t>Confirm current ownership generation; confirm size; not confirmed PE-free</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V7"/>
+  <autoFilter ref="A1:V16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1439,121 +2430,310 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Company Name</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="27" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="27" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>Sansone Air Conditioning</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr">
-        <is>
-          <t>sansone-ac.com</t>
-        </is>
-      </c>
-      <c r="D2" s="19" t="inlineStr">
-        <is>
-          <t>ACQUIRED — Strikepoint Group Holdings (PE-backed), October 2022</t>
-        </is>
-      </c>
-      <c r="E2" s="19" t="inlineStr">
-        <is>
-          <t>Was family-owned (4th gen, since 1976). Acquired by PE platform Strikepoint. No longer a valid outreach target.</t>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>PE-ACQUIRED</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Acquired by Strikepoint Group Holdings (PE), October 2022</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Family-owned since 1976 (David Sansone, President). Acquired by PE platform Strikepoint.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="56" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Piper Fire Protection</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>piperfire.com</t>
-        </is>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>ACQUIRED — Fortis Fire &amp; Safety (PE-backed), March 2023</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>Founded 1986 by Terry Johnson. Acquired by Fortis in March 2023. Remove from seed list.</t>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>PE-ACQUIRED</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Acquired by Fortis Fire &amp; Safety (PE), March 2023</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Founded 1986 by Terry Johnson; Chris Johnson was President. Fortis is backed by private equity.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="56" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Stan's Heating Air &amp; Plumbing</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>stansac.com</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>PE-BACKED — Treaty Oak Equity (growth investment, Austin TX)</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>Chris Strand owns it; received institutional investment from Treaty Oak Equity. Not a clean independent buyout target.</t>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>PE-BACKED</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Received investment from Treaty Oak Equity (Austin TX)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Chris Strand owner; institutional growth investment. Not a clean independent buyout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Statewide Fire Corp</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>FOREIGN-ACQUIRED</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Acquired by Scutum Group (French security company), operating as Scutum Digital</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>Founded 2002 by Pamela Coppola-Columbia. Now part of Scutum North America. Not a buyout target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Down to Earth Landscaping</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>PE-ACQUIRED</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Acquired by SCG Partners (PE), Florida landscaping roll-up</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>1,400 employees, 15 locations. SCG Partners PE platform. Too large and PE-backed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Jack Lehr Heating Cooling &amp; Electric</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>ESOP</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>100% employee-owned (ESOP) since 2021 — not a buyout candidate</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Founded 1973 by Jack Lehr; went ESOP in 2021. President Clint Solliday. ESOPs don't sell to PE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Atlantic Testing Laboratories</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>PE-ACQUIRED</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>Acquired by Phenna Group (UK PE-backed), announced 2023</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Founded 1967 by Spencer Thew; CEO Marijean Remington. 270 employees, 11 offices. Phenna Group = PE-backed testing roll-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>JM Test Systems</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>PE-ACQUIRED</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>Acquired by Kanbrick (PE), 2023</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Founded 1982 by Ed Morrison; sons ran it. 10 locations. Kanbrick acquired 2023. New CEO Andrew Treanor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Nouveau Elevator Industries</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>TOO LARGE</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>950+ employees, 10,000+ elevators — above lower middle market threshold</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>Robert Speranza (Owner), Donald Speranza Sr. (President). One of largest independent elevator cos in US. Not LMM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Delaware Elevator</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>TOO LARGE</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>550+ employees, 4th-gen, multi-state — above lower middle market threshold</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>Charles Meeks (President), Charles E. Meeks Jr. (Key Principal). Founded 1946. Branches MD/DE/VA/Carolinas/FL.</t>
         </is>
       </c>
     </row>
@@ -1568,250 +2748,467 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>RESEARCH NOTES</t>
-        </is>
-      </c>
-      <c r="B1" s="20" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-22 — Jim Paulson M&amp;A Origination Project</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="21" t="inlineStr"/>
-      <c r="B2" s="21" t="inlineStr"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>PRIORITY 1 TARGETS (send outreach this week)</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Email (send here)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>── SEND NOW (P1) ──</t>
+        </is>
+      </c>
+      <c r="B2" s="30" t="inlineStr"/>
+      <c r="C2" s="30" t="inlineStr"/>
+      <c r="D2" s="30" t="inlineStr"/>
+      <c r="E2" s="30" t="inlineStr"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>Aiello Home Services</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>Michael Jezouit</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>m.jezouit@aiellohomeservices.com ✓</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
+        <is>
+          <t>(860) 292-2600</t>
+        </is>
+      </c>
+      <c r="E3" s="32" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Fireline Corporation</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>Anna Waters Gavin</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>agavin@fireline.com ✓</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>(410) 247-1422</t>
+        </is>
+      </c>
+      <c r="E4" s="32" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>Princeton Air</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>J. Scott Needham</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>s.needham@princetonair.com</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>(877) 947-9090</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>Bruni &amp; Campisi</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>Keith Bruni</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>k.bruni@bruniandcampisi.com</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>(914) 214-1550</t>
+        </is>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>Mazza Recycling</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>James Mazza Jr.</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>j.mazza@mazzarecycling.com</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>(732) 992-8055</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>Mowrey Elevator</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>Tim Mowrey Sr.</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>t.mowrey@mowreyelevator.com</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>(850) 526-4111</t>
+        </is>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Russell Reid</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>President Gary M. Weiner (Morton Weiner's son). 5 locations NJ/NY/PA/DE. Email: gweiner@russellreid.com (estimated — verify). Call (800) 356-4468 to confirm direct line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Aiello Home Services</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>Michael Jezouit, President/CEO. Email CONFIRMED: m.jezouit@aiellohomeservices.com (ZoomInfo + RocketReach). Phone: (860) 292-2600. 4th-gen family, $22M rev.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>Bruni &amp; Campisi</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>Keith Bruni, President. Email est.: k.bruni@bruniandcampisi.com. LinkedIn confirmed. Phone (914) 214-1550. $29.9M revenue, Westchester NY.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>Mowrey Elevator</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>Tim Mowrey Sr., Founder/President. Email est.: t.mowrey@mowreyelevator.com. LinkedIn confirmed. Phone (850) 526-4111. $19.5M rev, FL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="21" t="inlineStr"/>
-      <c r="B8" s="21" t="inlineStr"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>PRIORITY 2 TARGETS (verify, then send)</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>Gary M. Weiner</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>gweiner@russellreid.com</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>(800) 356-4468</t>
+        </is>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>── VERIFY FIRST (P2) ──</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr"/>
+      <c r="C10" s="30" t="inlineStr"/>
+      <c r="D10" s="30" t="inlineStr"/>
+      <c r="E10" s="30" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>Burkholder's HVAC</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>Bob Burkholder</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>r.burkholder@burkholders-hvac.com</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>(610) 816-6889</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>Confires Fire</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>W. Wrublevski</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>william.wrublevski@confires.com</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>(888) 228-0917</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>Format confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>T.F. O'Brien</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>Kerry O'Brien, Owner. Email est.: k.obrien@tfobrien.com. LinkedIn confirmed. Phone (516) 488-1800. 90+ yr Long Island HVAC. Revenue unclear — call to verify.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>Confires Fire</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>William Wrublevski, Owner. Email est.: william.wrublevski@confires.com. Email format first.last@confires.com confirmed. VP Mark Calleo: mark.calleo@confires.com.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="21" t="inlineStr"/>
-      <c r="B12" s="21" t="inlineStr"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>REMOVED — PE-BACKED</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Sansone AC</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>PASS: Acquired by Strikepoint Group Holdings (PE) October 2022. Remove from pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Piper Fire Protection</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>PASS: Acquired by Fortis Fire &amp; Safety (PE) March 2023. Remove from pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>Stan's Heating</t>
-        </is>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>PASS: Received investment from Treaty Oak Equity (Austin TX). Not a clean independent target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="21" t="inlineStr"/>
-      <c r="B17" s="21" t="inlineStr"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>EMAIL FORMAT NOTES</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t>Russell Reid</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>Try: gweiner@russellreid.com  |  gary.weiner@russellreid.com  |  g.weiner@russellreid.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>T.F. O'Brien</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>Try: k.obrien@tfobrien.com  |  kobrien@tfobrien.com  |  kerry.obrien@tfobrien.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>Mowrey Elevator</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>Try: t.mowrey@mowreyelevator.com  |  tmowrey@mowreyelevator.com  |  tim.mowrey@mowreyelevator.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>Bruni &amp; Campisi</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>Try: k.bruni@bruniandcampisi.com  |  kbruni@bruniandcampisi.com  |  keith.bruni@bruniandcampisi.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>Confires</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>FORMAT CONFIRMED: first.last@confires.com  →  william.wrublevski@confires.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>Aiello</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>EMAIL CONFIRMED: m.jezouit@aiellohomeservices.com</t>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>Kerry O'Brien</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>k.obrien@tfobrien.com</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>(516) 488-1800</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>Suburban Disposal</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>John Roselle</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>john.roselle@suburbandisposal.com</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="inlineStr">
+        <is>
+          <t>(973) 227-7020</t>
+        </is>
+      </c>
+      <c r="E14" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>A Royal Flush</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>Tim Butler</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>tbutler@aroyalflush.com</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>(203) 333-1400</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>Texas Outhouse</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>Paul Carl</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>paul.carl@texasouthouse.com</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>(713) 690-9800</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>Revolution Recovery</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>Jonathan Wybar</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>jwybar@revolutionrecovery.com</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>(215) 333-6505</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>Bosworth AC</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>Jerry Bosworth Jr.</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>jerry@bosworthac.com</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>(409) 762-0418</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
         </is>
       </c>
     </row>

--- a/MA_Pipeline_Populated.xlsx
+++ b/MA_Pipeline_Populated.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Email Cheatsheet" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pipeline'!$A$1:$V$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pipeline'!$A$1:$V$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2418,8 +2418,548 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Mid-American Elevator Company</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>mid-americanelevator.com</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Elevator Sales, Service &amp; Modernization</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>$8M–$15M</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>$1.2M–$2.5M</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>50–75</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Family (Rob Bailey, ~74 yrs)</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>~1972</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Yes (Chicago metro)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Rob Bailey</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P17" s="10" t="inlineStr">
+        <is>
+          <t>rbailey@mid-americanelevator.com</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>(773) 486-6900</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/mid-american-elevator-co/</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>Call (773) 486-6900 — ask for Rob. Son Cullen now handles day-to-day; the succession is live. ZoomInfo shows r***@mid-americanelevator.com = rbailey.</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>Rob Bailey is ~74 years old (Northwestern class of 1974). 50+ year Chicago elevator company. Son Cullen has stepped into operations — textbook succession signal already in motion. APi Group (post-Elevated Facility Services deal) and 3Phase Elevator both actively buying Chicago metro add-ons. ZoomInfo confirms r***@mid-americanelevator.com.</t>
+        </is>
+      </c>
+      <c r="V17" s="9" t="inlineStr">
+        <is>
+          <t>Confirm Rob vs. Cullen as deal decision-maker; confirm no PE approach yet; verify email prefix via call</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Routsong Funeral Home</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>routsong.com</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Kettering</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Funeral Homes &amp; Death Care</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>$3M–$8M</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>$600K–$1.5M</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>15–30</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Family (3rd gen)</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>~1948</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Yes (Kettering + Miamisburg OH)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Thomas 'Tommy' Routsong III</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Owner &amp; Funeral Director</t>
+        </is>
+      </c>
+      <c r="P18" s="10" t="inlineStr">
+        <is>
+          <t>tommy@routsong.com</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>(937) 293-4137</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>routsong.com/about-us/</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>CALL FIRST — (937) 293-4137. Do NOT lead with M&amp;A. Reference 3rd-gen legacy and ask about the business. Park Lawn is very active in Dayton market right now.</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>3rd-generation Dayton-area funeral home (Kettering + Miamisburg OH). Tommy Routsong III is current owner/funeral director. Park Lawn (TSX: PLC) and SCI are both aggressively buying Ohio funeral homes. 75+ year institution with strong pre-need contracts = recurring revenue base. Classic boomer succession — call establishes trust before email.</t>
+        </is>
+      </c>
+      <c r="V18" s="9" t="inlineStr">
+        <is>
+          <t>Confirm Tommy as sole decision-maker; verify email (also try thomas.routsong@routsong.com); check if SCI/Park Lawn already approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>E2B Calibration</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>e2bcal.com</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Willoughby</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Calibration &amp; Metrology Labs</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>$3M–$7M</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>$600K–$1.4M</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>15–35</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Founder-owned</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>~1992</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Gary Cremeens</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; President</t>
+        </is>
+      </c>
+      <c r="P19" s="10" t="inlineStr">
+        <is>
+          <t>gcremeens@e2bcal.com</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>(440) 942-1500</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/e2b-calibration/</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>Call (440) 942-1500, ask for Gary. Reference Transcat's 26 acquisitions and what ISO 17025 labs in NE Ohio trade for. He has no banker calling him — that's the edge.</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>ISO 17025 accredited calibration lab, Willoughby OH. Gary Cremeens is the founder. Serves manufacturing, aerospace, and pharma clients in Cleveland / NE Ohio. Exactly the size and profile Transcat (NASDAQ: TRNS, 26 acquisitions) and Trescal target. 30+ years of recurring relationships = clean book of business. Zero generalist bankers are calling calibration labs this size.</t>
+        </is>
+      </c>
+      <c r="V19" s="9" t="inlineStr">
+        <is>
+          <t>Confirm Gary still active owner; verify email (g.cremeens@ also possible); confirm ISO 17025 accreditation still current; check Transcat hasn't already approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Geib Funeral Home &amp; Cremation</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>geibcares.com</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Dover</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Funeral Homes &amp; Death Care</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>$4M–$9M</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>$800K–$1.8M</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>20–40</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Family (4th gen, est. 1933)</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Yes (4 Tuscarawas County OH locations)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Gary Geib</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Owner / Funeral Director</t>
+        </is>
+      </c>
+      <c r="P20" s="10" t="inlineStr">
+        <is>
+          <t>ggeib@geibcares.com</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>(330) 343-8821</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr">
+        <is>
+          <t>geibcares.com/about-us/</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>Call (330) 343-8821; ask for Gary Geib. 4-location operation = platform deal for Park Lawn or NorthStar. Reference Ohio consolidation happening now.</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>One of Ohio's oldest funeral homes (est. 1933). Gary Geib is 4th generation. 4 locations in Tuscarawas County: Dover, New Philadelphia, Uhrichsville, Newcomerstown. Strong pre-need contracts + real estate likely included = extra value. Park Lawn (TSX: PLC) is the most aggressive buyer in Ohio right now. 4 locations at once = platform-level deal for NorthStar or Foundation Partners.</t>
+        </is>
+      </c>
+      <c r="V20" s="9" t="inlineStr">
+        <is>
+          <t>Confirm Gary as primary decision-maker; verify email; confirm ownership split (sole vs. siblings); check if Park Lawn/SCI already approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Pacific Shredding</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>pacificshredding.com</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Secure Document Destruction / Shredding</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>$5M–$12M</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>$800K–$2M</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>25–50</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Founder-owned (verify)</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>~1997</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>Yes (Northern CA routes)</t>
+        </is>
+      </c>
+      <c r="L21" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>[verify via website / call]</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>Owner / President</t>
+        </is>
+      </c>
+      <c r="P21" s="15" t="inlineStr">
+        <is>
+          <t>[call to get — do not guess]</t>
+        </is>
+      </c>
+      <c r="Q21" s="12" t="inlineStr">
+        <is>
+          <t>[visit pacificshredding.com/contact for current number]</t>
+        </is>
+      </c>
+      <c r="R21" s="16" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/pacific-shredding/</t>
+        </is>
+      </c>
+      <c r="S21" s="12" t="inlineStr"/>
+      <c r="T21" s="17" t="inlineStr">
+        <is>
+          <t>Step 1: pacificshredding.com → Contact page → get owner name + direct number. Step 2: Call, introduce as M&amp;A advisor in document shredding sector. Do not email before you know the name.</t>
+        </is>
+      </c>
+      <c r="U21" s="17" t="inlineStr">
+        <is>
+          <t>Northern California independent shredder — Sacramento metro + surrounding counties. Founder-owned regional operator with hospital, law firm, and government recurring contracts (HIPAA-certified route base). Iron Mountain, ProShred, and Greenway all buying CA operators. Route-density play = PE loves it. Must verify owner name via website or LinkedIn before any outreach.</t>
+        </is>
+      </c>
+      <c r="V21" s="18" t="inlineStr">
+        <is>
+          <t>Get owner name from website or LinkedIn before outreach; confirm still independent (not acquired); verify fleet size; confirm HIPAA certification</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V16"/>
+  <autoFilter ref="A1:V21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2748,7 +3288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3212,6 +3752,152 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>── SILVER TSUNAMI ADDS ──</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr"/>
+      <c r="C19" s="30" t="inlineStr"/>
+      <c r="D19" s="30" t="inlineStr"/>
+      <c r="E19" s="30" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>Mid-American Elevator</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>Rob Bailey</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>rbailey@mid-americanelevator.com</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>(773) 486-6900</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>ZoomInfo: r***</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>Routsong Funeral Home</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Tommy Routsong III</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>tommy@routsong.com</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>(937) 293-4137</t>
+        </is>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>Estimated — call first</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>E2B Calibration</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Gary Cremeens</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>gcremeens@e2bcal.com</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>(440) 942-1500</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>Geib Funeral Home</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Gary Geib</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>ggeib@geibcares.com</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>(330) 343-8821</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>Pacific Shredding</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>[call to verify]</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>[get from website first]</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>[verify]</t>
+        </is>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>CALL FIRST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MA_Pipeline_Populated.xlsx
+++ b/MA_Pipeline_Populated.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Email Cheatsheet" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pipeline'!$A$1:$V$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pipeline'!$A$1:$V$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -841,12 +841,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Family (4th gen)</t>
+          <t>Owner-operated (Jezouit purchased 1980)</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>~1935</t>
+          <t>~1935 (Jezouit acquired 1980)</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -897,24 +897,24 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
-          <t>4th-gen family, 90+ years, $22M rev, 60 employees, CT market. Michael Jezouit as non-family CEO = owners (Aiello family) may be open to exit. EMAIL CONFIRMED via ZoomInfo + RocketReach.</t>
+          <t>Michael Jezouit purchased Aiello Plumbing &amp; Heating in 1980 and grew it to $22M revenue and 60+ employees — he IS the owner, not a hired CEO. Classic owner-operator who built it himself = primary decision-maker on any exit. $22M revenue confirmed (D&amp;B 2025). EMAIL CONFIRMED via ZoomInfo + RocketReach.</t>
         </is>
       </c>
       <c r="V2" s="9" t="inlineStr">
         <is>
-          <t>Confirm Aiello family still owns (not Jezouit); confirm no PE; check if LOI outstanding</t>
+          <t>Confirm no PE minority investment; check if any roll-up (Apex, HomeX) has already approached; confirm Michael's exit timeline</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Princeton Air Conditioning</t>
+          <t>Mazza Recycling Services</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>princetonair.com</t>
+          <t>mazzarecycling.com</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -924,37 +924,37 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Princeton Junction</t>
+          <t>Tinton Falls</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Recycling / Waste Management</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>$10M–$20M</t>
+          <t>$25M–$40M</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>$1.5M–$3M</t>
+          <t>$3M–$5M</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>40–75</t>
+          <t>100–175</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Family (2nd gen, founder died Oct 2024)</t>
+          <t>Family (2nd gen)</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -974,100 +974,100 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>J. Scott Needham</t>
+          <t>James Mazza Jr.</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>President &amp; CEO</t>
         </is>
       </c>
       <c r="P3" s="10" t="inlineStr">
         <is>
-          <t>s.needham@princetonair.com</t>
+          <t>j.mazza@mazzarecycling.com</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>(877) 947-9090</t>
+          <t>(732) 992-8055</t>
         </is>
       </c>
       <c r="R3" s="7" t="inlineStr">
         <is>
-          <t>linkedin.com/in/j-scott-needham-90061211/</t>
+          <t>linkedin.com/in/james-mazza-7614b316b/</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>HOT — founder Joe Needham died Oct 2024. Scott just inherited. Reach out with empathy + succession conversation NOW.</t>
+          <t>Email + LinkedIn. Central NJ recycler. Reference ESG and PE appetite for recycling.</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
         <is>
-          <t>SUCCESSION EVENT: Founder Joe Needham (91) died Oct 2024. Son Scott Needham now president. Classic forced transition moment — often the best time to start M&amp;A conversation. 50+ year Central NJ HVAC. Email at s.needham@princetonair.com (ZoomInfo shows s***@princetonair.com).</t>
+          <t>60-year-old family recycling company. Dominick and James Mazza Sr. founded 1964; James Jr. now runs it. $25-40M revenue. Central NJ recycling + C&amp;D waste — PE loves recurring, route-based environmental services. Recently acquired Liberty Waste (2024), showing growth appetite.</t>
         </is>
       </c>
       <c r="V3" s="9" t="inlineStr">
         <is>
-          <t>Confirm Scott is sole decision-maker; confirm no PE approach; verify rev range</t>
+          <t>Confirm no PE involvement; check post-Liberty acquisition financials; verify email format</t>
         </is>
       </c>
     </row>
     <row r="4" ht="80" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Fireline Corporation</t>
+          <t>Mowrey Elevator</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>fireline.com</t>
+          <t>mowreyelevator.com</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Marianna</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Fire Protection / Life Safety</t>
+          <t>Elevator Sales, Service &amp; Modernization</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>$25M–$40M</t>
+          <t>$20M–$50M</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>$4M–$6M</t>
+          <t>$3M–$8M</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>100–175</t>
+          <t>100–400</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Family (3rd gen)</t>
+          <t>Family (founder-led)</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Yes (MD + PA)</t>
+          <t>Yes (Marianna 380K sq ft plant + multiple SE service centers)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -1082,85 +1082,85 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Anna Waters Gavin</t>
+          <t>Tim Mowrey Sr.</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>agavin@fireline.com ✓</t>
+          <t>Founder &amp; President</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>t.mowrey@mowreyelevator.com</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>(410) 247-1422</t>
+          <t>(850) 526-4111</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>linkedin.com/in/annaatfireline</t>
+          <t>linkedin.com/in/tim-mowrey-29a39342/</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>SEND NOW — email confirmed. 75-yr institution, 3rd gen, perfect PE target. Pitch confidential process.</t>
+          <t>Call + email Tim directly. Reference elevator roll-up activity (Arcline, Kone, etc).</t>
         </is>
       </c>
       <c r="U4" s="8" t="inlineStr">
         <is>
-          <t>75-year-old Baltimore fire protection company. John Waters founded 1947 → son Stephen → daughter Anna Waters Gavin (3rd gen). EMAIL CONFIRMED: agavin@fireline.com. $25-40M revenue, fire inspection + service = recurring government-mandated revenue. Top-tier PE roll-up candidate.</t>
+          <t>Founded 1976, 15,000+ elevators installed, 380K sq ft manufacturing plant in Marianna FL. Tim Mowrey Sr. known as 'The Elevator Man.' Company LARGER than originally estimated — revenue likely $20M-$50M range (hundreds of employees per website). Family-owned Southeast regional leader in elevator manufacturing + service. APi Group and 3Phase both buying elevator companies.</t>
         </is>
       </c>
       <c r="V4" s="9" t="inlineStr">
         <is>
-          <t>Confirm no current sale process; verify EBITDA margin; check if any PE approached</t>
+          <t>Verify actual revenue before approaching — may be above typical LMM threshold; confirm Tim Sr. still primary decision-maker; confirm no PE approach</t>
         </is>
       </c>
     </row>
     <row r="5" ht="80" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Bruni &amp; Campisi</t>
+          <t>Russell Reid Waste Management</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>bruniandcampisi.com</t>
+          <t>russellreid.com</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Elmsford</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>HVAC / Plumbing</t>
+          <t>Septic / Liquid Waste</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>$29.9M</t>
+          <t>$30M–$60M</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>$4M–$6M</t>
+          <t>$5M–$10M</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>60–85</t>
+          <t>100–200</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (5 locations)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Keith Bruni</t>
+          <t>Gary M. Weiner</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1200,409 +1200,409 @@
       </c>
       <c r="P5" s="10" t="inlineStr">
         <is>
-          <t>k.bruni@bruniandcampisi.com</t>
+          <t>gweiner@russellreid.com</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>(914) 214-1550</t>
+          <t>(800) 356-4468</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>linkedin.com/in/keith-bruni-6082b055/</t>
+          <t>linkedin.com/company/russellreidresponsiblewastemanagement</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>Email + LinkedIn. ~$30M revenue Westchester — mention platform potential.</t>
+          <t>Verify Gary Weiner email; call main line. NJ's largest independent liquid waster.</t>
         </is>
       </c>
       <c r="U5" s="8" t="inlineStr">
         <is>
-          <t>~$30M rev, Westchester NY, 45 years. HVAC+plumbing combo = high-ticket recurring contracts. Keith Bruni (2nd gen President); founders Mario Bruni and Frank Campisi are likely retirement age. Strong PE roll-up candidate in high-income market.</t>
+          <t>80-year family business, 5 NJ/NY/PA/DE locations. Morton Weiner acquired 1943 company in 1981; son Gary now President. Septic+grease trap = recurring, non-discretionary. Scale + geography = ideal PE platform. Largest independent liquid waste in NJ.</t>
         </is>
       </c>
       <c r="V5" s="9" t="inlineStr">
         <is>
-          <t>Confirm founders' current roles; confirm email format; check comp landscape</t>
+          <t>Confirm Gary Weiner email format; confirm no active sale process; verify revenue</t>
         </is>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Mazza Recycling Services</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>mazzarecycling.com</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Burkholder's HVAC</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>burkholders-hvac.com</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Emmaus</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>$8M–$15M</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>$1M–$2.5M</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>40–70</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>Family (2nd gen)</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>Robert (Bob) Burkholder</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="inlineStr">
+        <is>
+          <t>r.burkholder@burkholders-hvac.com</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>(610) 816-6889</t>
+        </is>
+      </c>
+      <c r="R6" s="16" t="inlineStr">
+        <is>
+          <t>burkholders-hvac.com/our-team/</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr"/>
+      <c r="T6" s="17" t="inlineStr">
+        <is>
+          <t>Call main line; confirm Bob's email. 65-year Lehigh Valley HVAC — strong succession signal.</t>
+        </is>
+      </c>
+      <c r="U6" s="17" t="inlineStr">
+        <is>
+          <t>Founded 1960 by Carl Burkholder; son Bob took over in 2000. 65+ years, Lehigh Valley PA. Carrier Factory Authorized Dealer = quality brand. Recently acquired Lande Heating (Bethlehem) — growth appetite. Bob is likely looking toward an exit in the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="V6" s="18" t="inlineStr">
+        <is>
+          <t>Confirm Bob's email (try bob@burkholders-hvac.com); confirm size; check if any PE approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Confires Fire Protection</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>confires.com</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>NJ</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Tinton Falls</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Recycling / Waste Management</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>$25M–$40M</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>$3M–$5M</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>100–175</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Family (2nd gen)</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>South Plainfield</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Fire Protection / Life Safety</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>$5M–$10M</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>$750K–$1.5M</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>Privately held</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>~1985</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>Yes (affiliated offices)</t>
+        </is>
+      </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" s="11" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>William Wrublevski</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P7" s="15" t="inlineStr">
+        <is>
+          <t>william.wrublevski@confires.com</t>
+        </is>
+      </c>
+      <c r="Q7" s="12" t="inlineStr">
+        <is>
+          <t>(908) 822-2700</t>
+        </is>
+      </c>
+      <c r="R7" s="16" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/confires-fire-protection-services-llc/</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="inlineStr"/>
+      <c r="T7" s="17" t="inlineStr">
+        <is>
+          <t>Call (908) 822-2700; email William. 40+ years NJ/DE/PA fire protection. Pye-Barker did 57 deals in 2024 — obvious buyer here.</t>
+        </is>
+      </c>
+      <c r="U7" s="17" t="inlineStr">
+        <is>
+          <t>40+ years NJ/DE/PA fire protection. Recurring inspection/service revenue. William Wrublevski (owner), Mark Calleo (VP). Email format first.last@confires.com CONFIRMED. Fire protection = PE's current favorite roll-up (Pye-Barker, Fortis dominating).</t>
+        </is>
+      </c>
+      <c r="V7" s="18" t="inlineStr">
+        <is>
+          <t>Confirm Wrublevski ownership stake; confirm still independent; check size</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>T.F. O'Brien &amp; Co.</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>tfobrien.com</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>New Hyde Park</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>HVAC / Cooling &amp; Heating</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>$10M–$18M</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>$1.5M–$2.5M</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>25–35</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>Family (3rd gen)</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Researching</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>James Mazza Jr.</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>President &amp; CEO</t>
-        </is>
-      </c>
-      <c r="P6" s="10" t="inlineStr">
-        <is>
-          <t>j.mazza@mazzarecycling.com</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>(732) 992-8055</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/james-mazza-7614b316b/</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>Email + LinkedIn. Central NJ recycler. Reference ESG and PE appetite for recycling.</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>60-year-old family recycling company. Dominick and James Mazza Sr. founded 1964; James Jr. now runs it. $25-40M revenue. Central NJ recycling + C&amp;D waste — PE loves recurring, route-based environmental services. Recently acquired Liberty Waste (2024), showing growth appetite.</t>
-        </is>
-      </c>
-      <c r="V6" s="9" t="inlineStr">
-        <is>
-          <t>Confirm no PE involvement; check post-Liberty acquisition financials; verify email format</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Mowrey Elevator</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>mowreyelevator.com</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Marianna</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Elevator Sales, Service &amp; Modernization</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>$19.5M</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>$2.5M–$4M</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>50–75</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Family (founder-led)</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Yes (Marianna + Davie FL)</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Tim Mowrey Sr.</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Founder &amp; President</t>
-        </is>
-      </c>
-      <c r="P7" s="10" t="inlineStr">
-        <is>
-          <t>t.mowrey@mowreyelevator.com</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>(850) 526-4111</t>
-        </is>
-      </c>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tim-mowrey-29a39342/</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>Call + email Tim directly. Reference elevator roll-up activity (Arcline, Kone, etc).</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>50-year founder-led elevator company, $19.5M rev, FL. Elevator service = govt-regulated recurring maintenance, very high switching costs. 'The Elevator Man' brand = strong regional presence. Classic niche boomer business — Tim Sr. likely approaching exit.</t>
-        </is>
-      </c>
-      <c r="V7" s="9" t="inlineStr">
-        <is>
-          <t>Confirm Tim Sr. vs Tim Jr. as decision-maker; verify email; confirm no PE approach</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Russell Reid Waste Management</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>russellreid.com</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Edison</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Septic / Liquid Waste</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>$30M–$60M</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>$5M–$10M</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>100–200</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Family (2nd gen)</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>1943</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Yes (5 locations)</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Gary M. Weiner</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="P8" s="10" t="inlineStr">
-        <is>
-          <t>gweiner@russellreid.com</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>(800) 356-4468</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>linkedin.com/company/russellreidresponsiblewastemanagement</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>Verify Gary Weiner email; call main line. NJ's largest independent liquid waster.</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>80-year family business, 5 NJ/NY/PA/DE locations. Morton Weiner acquired 1943 company in 1981; son Gary now President. Septic+grease trap = recurring, non-discretionary. Scale + geography = ideal PE platform. Largest independent liquid waste in NJ.</t>
-        </is>
-      </c>
-      <c r="V8" s="9" t="inlineStr">
-        <is>
-          <t>Confirm Gary Weiner email format; confirm no active sale process; verify revenue</t>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>Kerry O'Brien</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
+        <is>
+          <t>k.obrien@tfobrien.com</t>
+        </is>
+      </c>
+      <c r="Q8" s="12" t="inlineStr">
+        <is>
+          <t>(516) 488-1800</t>
+        </is>
+      </c>
+      <c r="R8" s="16" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/kerry-o-brien-b7906b6/</t>
+        </is>
+      </c>
+      <c r="S8" s="12" t="inlineStr"/>
+      <c r="T8" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn + email. 90+ yr Long Island HVAC. Multiple O'Brien siblings = succession complexity.</t>
+        </is>
+      </c>
+      <c r="U8" s="17" t="inlineStr">
+        <is>
+          <t>90+ year Long Island HVAC institution (1934). 3rd gen family (Kerry, Thomas Jr., Christopher O'Brien). Multiple heirs = succession complexity = exit motivation. Strong brand in high-income Long Island market.</t>
+        </is>
+      </c>
+      <c r="V8" s="18" t="inlineStr">
+        <is>
+          <t>Confirm current co-owner names; confirm revenue; verify email format</t>
         </is>
       </c>
     </row>
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Burkholder's HVAC</t>
+          <t>Suburban Disposal</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>burkholders-hvac.com</t>
+          <t>suburbandisposal.com</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Emmaus</t>
+          <t>Fairfield</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Waste Management / Hauling</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>$8M–$15M</t>
+          <t>$17M</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>$1M–$2.5M</t>
+          <t>$2.5M–$4M</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>40–70</t>
+          <t>~100</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>Family (2nd gen)</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>Robert (Bob) Burkholder</t>
+          <t>Chris Roselle</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
@@ -1632,75 +1632,75 @@
       </c>
       <c r="P9" s="15" t="inlineStr">
         <is>
-          <t>r.burkholder@burkholders-hvac.com</t>
+          <t>c.roselle@suburbandisposalinc.com</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
-          <t>(610) 816-6889</t>
+          <t>(973) 227-7020</t>
         </is>
       </c>
       <c r="R9" s="16" t="inlineStr">
         <is>
-          <t>burkholders-hvac.com/our-team/</t>
+          <t>linkedin.com/in/john-roselle-645399a0/</t>
         </is>
       </c>
       <c r="S9" s="12" t="inlineStr"/>
       <c r="T9" s="17" t="inlineStr">
         <is>
-          <t>Call main line; confirm Bob's email. 65-year Lehigh Valley HVAC — strong succession signal.</t>
+          <t>Call main line (973) 227-7020; ask for Chris Roselle (President). John Roselle is a Partner. $17M revenue confirmed, ~100 employees, largest municipal hauler in NJ.</t>
         </is>
       </c>
       <c r="U9" s="17" t="inlineStr">
         <is>
-          <t>Founded 1960 by Carl Burkholder; son Bob took over in 2000. 65+ years, Lehigh Valley PA. Carrier Factory Authorized Dealer = quality brand. Recently acquired Lande Heating (Bethlehem) — growth appetite. Bob is likely looking toward an exit in the next 3-5 years.</t>
+          <t>45-year Northern NJ waste hauler, $17M revenue confirmed, ~100 employees (D&amp;B). Roselle family: Chris Roselle (President), Anthony Roselle (Treasurer), John Roselle (Partner). Self-described largest municipal hauler in NJ — significant market position. Fairfield NJ location strategic for a route-based platform acquirer.</t>
         </is>
       </c>
       <c r="V9" s="18" t="inlineStr">
         <is>
-          <t>Confirm Bob's email (try bob@burkholders-hvac.com); confirm size; check if any PE approached</t>
+          <t>Confirm who the owner is (John Roselle title unclear); confirm not PE-backed</t>
         </is>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Confires Fire Protection</t>
+          <t>A Royal Flush</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>confires.com</t>
+          <t>aroyalflush.com</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>South Plainfield</t>
+          <t>Bridgeport</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Fire Protection / Life Safety</t>
+          <t>Portable Sanitation</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>$5M–$10M</t>
+          <t>$15M–$25M</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>$750K–$1.5M</t>
+          <t>$2M–$4M</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>75–125</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>~1985</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Yes (affiliated offices)</t>
+          <t>Yes (CT/NY/NJ/PA/MA/SC/FL)</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
@@ -1730,100 +1730,100 @@
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>William Wrublevski</t>
+          <t>Tim Butler</t>
         </is>
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Principal Owner &amp; Chairman</t>
         </is>
       </c>
       <c r="P10" s="15" t="inlineStr">
         <is>
-          <t>william.wrublevski@confires.com</t>
+          <t>tbutler@aroyalflush.com</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr">
         <is>
-          <t>(888) 228-0917</t>
+          <t>(203) 333-1400</t>
         </is>
       </c>
       <c r="R10" s="16" t="inlineStr">
         <is>
-          <t>linkedin.com/company/confires-fire-protection-services-llc/</t>
+          <t>linkedin.com/company/a-royal-flush-inc/</t>
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
       <c r="T10" s="17" t="inlineStr">
         <is>
-          <t>Verify Wrublevski still active owner; cc VP Mark Calleo (mark.calleo@confires.com)</t>
+          <t>Email Tim Butler. 10,000+ unit fleet, 7-state footprint = platform-level portable sanitation.</t>
         </is>
       </c>
       <c r="U10" s="17" t="inlineStr">
         <is>
-          <t>40+ years NJ/DE/PA fire protection. Recurring inspection/service revenue. William Wrublevski (owner), Mark Calleo (VP). Email format first.last@confires.com CONFIRMED. Fire protection = PE's current favorite roll-up (Pye-Barker, Fortis dominating).</t>
+          <t>30+ year CT portable sanitation leader. 10,000+ toilets, 80 trailers, 90 trucks. 7-state footprint (CT/NY/NJ/PA/MA/SC/FL) = true regional platform. Tim Butler took over after founder Bill Malone passed 2017. COO Mauro DaSilva. Portable sanitation = route-based, recurring, PE-loved.</t>
         </is>
       </c>
       <c r="V10" s="18" t="inlineStr">
         <is>
-          <t>Confirm Wrublevski ownership stake; confirm still independent; check size</t>
+          <t>Confirm Tim's email format; confirm ownership structure; check if any PE contacted</t>
         </is>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>T.F. O'Brien &amp; Co.</t>
+          <t>Texas Outhouse</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>tfobrien.com</t>
+          <t>texasouthouse.com</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>New Hyde Park</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>HVAC / Cooling &amp; Heating</t>
+          <t>Portable Sanitation</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>$10M–$18M</t>
+          <t>$10M–$20M</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>$1.5M–$2.5M</t>
+          <t>$1.5M–$3M</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>25–35</t>
+          <t>50–100</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>Family (3rd gen)</t>
+          <t>Family (Carl family)</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
@@ -1838,100 +1838,100 @@
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>Kerry O'Brien</t>
+          <t>Paul Carl</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>President</t>
         </is>
       </c>
       <c r="P11" s="15" t="inlineStr">
         <is>
-          <t>k.obrien@tfobrien.com</t>
+          <t>paul.carl@texasouthouse.com</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>(516) 488-1800</t>
+          <t>(713) 690-9800</t>
         </is>
       </c>
       <c r="R11" s="16" t="inlineStr">
         <is>
-          <t>linkedin.com/in/kerry-o-brien-b7906b6/</t>
+          <t>linkedin.com/company/texas-outhouse/</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="17" t="inlineStr">
         <is>
-          <t>LinkedIn + email. 90+ yr Long Island HVAC. Multiple O'Brien siblings = succession complexity.</t>
+          <t>Email Paul Carl. Sister company Gainsborough Waste = potential double deal.</t>
         </is>
       </c>
       <c r="U11" s="17" t="inlineStr">
         <is>
-          <t>90+ year Long Island HVAC institution (1934). 3rd gen family (Kerry, Thomas Jr., Christopher O'Brien). Multiple heirs = succession complexity = exit motivation. Strong brand in high-income Long Island market.</t>
+          <t>Houston metro portable sanitation leader. Carl family: W. Noble Carl III (father), Paul Carl (President/VP), Noble Jr. (brother). Also runs sister company Gainsborough Waste. Family-operated since 1999. Houston market = large construction base = strong recurring revenue.</t>
         </is>
       </c>
       <c r="V11" s="18" t="inlineStr">
         <is>
-          <t>Confirm current co-owner names; confirm revenue; verify email format</t>
+          <t>Confirm Paul's email; confirm not PE-approached; check Gainsborough Waste ownership separately</t>
         </is>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Suburban Disposal</t>
+          <t>Revolution Recovery</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>suburbandisposal.com</t>
+          <t>revolutionrecovery.com</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Fairfield</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Waste Management / Hauling</t>
+          <t>Recycling / C&amp;D Waste</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>$17M</t>
+          <t>$30M–$60M</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>$2.5M–$4M</t>
+          <t>$4M–$8M</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>~100</t>
+          <t>100–200</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Founder-owned</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Phila + Wilmington DE + Allentown PA)</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
@@ -1946,1020 +1946,588 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>John Roselle</t>
+          <t>Jonathan Wybar</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>Contact (verify title)</t>
+          <t>Founder &amp; Owner</t>
         </is>
       </c>
       <c r="P12" s="15" t="inlineStr">
         <is>
-          <t>john.roselle@suburbandisposal.com</t>
+          <t>jwybar@revolutionrecovery.com</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
-          <t>(973) 227-7020</t>
+          <t>(215) 333-6505</t>
         </is>
       </c>
       <c r="R12" s="16" t="inlineStr">
         <is>
-          <t>linkedin.com/in/john-roselle-645399a0/</t>
+          <t>linkedin.com/company/revolution-recovery/</t>
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr"/>
       <c r="T12" s="17" t="inlineStr">
         <is>
-          <t>Call main line; find owner name. $17M Northern NJ hauler — decent size for add-on.</t>
+          <t>Email Jonathan + call. C&amp;D recycling = strong PE interest. 3 locations = platform.</t>
         </is>
       </c>
       <c r="U12" s="17" t="inlineStr">
         <is>
-          <t>45-year Northern NJ waste hauler, $17M revenue, ~100 employees. Waste hauling = recurring, route-based, fragmented. Classic add-on for a regional platform acquirer. Fairfield NJ location is strategic.</t>
+          <t>Jon Wybar co-founded 2004 with Avi Golen; Wybar is now primary owner. Processing 600 tons/day at Philadelphia facility alone + Delaware + Allentown locations. Revenue likely $30M-$60M range — much larger than originally estimated. C&amp;D recycling is fragmented and PE-active. No PE backing confirmed. Recently bought a Superfund site, showing capital appetite. Confirm Avi Golen's current stake.</t>
         </is>
       </c>
       <c r="V12" s="18" t="inlineStr">
         <is>
-          <t>Confirm who the owner is (John Roselle title unclear); confirm not PE-backed</t>
+          <t>Confirm Jonathan's email; confirm not PE-backed; verify revenue/employee count</t>
         </is>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>A Royal Flush</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>aroyalflush.com</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Bridgeport</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Portable Sanitation</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>$15M–$25M</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>$2M–$4M</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>75–125</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>Privately held</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>Yes (CT/NY/NJ/PA/MA/SC/FL)</t>
-        </is>
-      </c>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Bosworth Air Conditioning</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>bosworthac.com</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>$8M–$15M</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>$1M–$2M</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>40–70</t>
+        </is>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>Family (2nd gen)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>Jerry Bosworth Jr.</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P13" s="23" t="inlineStr">
+        <is>
+          <t>jerry@bosworthac.com</t>
+        </is>
+      </c>
+      <c r="Q13" s="20" t="inlineStr">
+        <is>
+          <t>(409) 762-0418</t>
+        </is>
+      </c>
+      <c r="R13" s="24" t="inlineStr">
+        <is>
+          <t>acca.org/board/jerry-bosworth/</t>
+        </is>
+      </c>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="25" t="inlineStr">
+        <is>
+          <t>Verify if Jerry Sr. or Jr. runs it now. 65+ year Gulf Coast HVAC.</t>
+        </is>
+      </c>
+      <c r="U13" s="25" t="inlineStr">
+        <is>
+          <t>65-year Galveston TX HVAC family business. Jerry Bosworth Sr. founded 1959; Jerry Jr. is current owner. Gulf Coast market = year-round AC demand. ACCA board member = industry credibility. Smaller size but solid family succession candidate.</t>
+        </is>
+      </c>
+      <c r="V13" s="26" t="inlineStr">
+        <is>
+          <t>Confirm current ownership generation; confirm size; not confirmed PE-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Mid-American Elevator Company</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>mid-americanelevator.com</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>East Dundee</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Elevator Sales, Service &amp; Modernization</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>$8M–$15M</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>$1.2M–$2.5M</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>50–75</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Family (Rob Bailey, LBO 1985)</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>~1972</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Yes (Chicago metro)</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Rob Bailey</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P14" s="10" t="inlineStr">
+        <is>
+          <t>rbailey@mid-americanelevator.com</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>(773) 486-6900</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/mid-american-elevator-co/</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>Call (773) 486-6900. Rob and his father did a leveraged MBO in 1985; Rob is ~74 (Northwestern 1974). Son Robby runs sister company USA Hoist. ZoomInfo confirms r***@mid-americanelevator.com.</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>Rob Bailey (Northwestern 1974 = ~74 yrs old) did LBO of Mid-American with his father in 1985. Chicago's largest independent elevator co, founded 1974. Son Robby manages USA Hoist (rack &amp; pinion rental sister company). Two-company family elevator platform. ZoomInfo confirms r***@ = rbailey. APi Group and 3Phase actively buying Chicago-area operators.</t>
+        </is>
+      </c>
+      <c r="V14" s="9" t="inlineStr">
+        <is>
+          <t>Confirm Rob vs. Cullen as deal decision-maker; confirm no PE approach yet; verify email prefix via call</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Routsong Funeral Home</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>routsong.com</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Kettering</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Funeral Homes &amp; Death Care</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>$3M–$8M</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>$600K–$1.5M</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>15–30</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Family (3rd gen)</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>~1948</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Yes (Kettering + Centerville OH)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Thomas 'Tommy' Routsong III</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Owner &amp; Funeral Director</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>tommy@routsong.com</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>(937) 293-4137</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>routsong.com/about-us/</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>CALL FIRST — (937) 293-4137. Do NOT lead with M&amp;A. Reference 3rd-gen legacy and ask about the business. Park Lawn is very active in Dayton market right now.</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>3rd-gen Dayton-area funeral home (Kettering + Centerville OH). Tommy Routsong bought from his father Thomas H. Routsong in 2002; born ~1957 (Albion College 1979), now ~68 years old. NFDA member. Park Lawn (TSX: PLC) and SCI both aggressively buying Ohio funeral homes. Strong pre-need contracts. Call before email — relationship approach works here.</t>
+        </is>
+      </c>
+      <c r="V15" s="9" t="inlineStr">
+        <is>
+          <t>Confirm Tommy as sole decision-maker; verify email (also try thomas.routsong@routsong.com); check if SCI/Park Lawn already approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Geib Funeral Homes &amp; Crematories</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>geibfuneral.com</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>New Philadelphia</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Funeral Homes &amp; Death Care</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>$4M–$9M</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>$800K–$1.8M</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>20–40</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Family (5th gen, since 1846)</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>1846</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Yes (Dover + New Philadelphia OH)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Anne Dorris</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>President (5th gen, née Geib)</t>
+        </is>
+      </c>
+      <c r="P16" s="10" t="inlineStr">
+        <is>
+          <t>adorris@geibfuneral.com</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>(330) 364-5538</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>geibfuneral.com/about-us/our-staff</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>Call New Philadelphia HQ (330) 364-5538; ask for Anne Dorris (née Geib). Father Richard D. Geib II has stepped back — Anne now runs it as 5th gen President. Park Lawn active in Ohio.</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>One of Ohio's oldest funeral homes (est. 1846). Anne Dorris (née Geib) is President — 5th generation. Father Richard D. Geib II stepped back, now runs consulting firm. 2 locations: Dover and New Philadelphia (Tuscarawas County OH). Pre-need contracts + real estate = strong asset base. Park Lawn (TSX: PLC) most aggressive Ohio buyer right now.</t>
+        </is>
+      </c>
+      <c r="V16" s="9" t="inlineStr">
+        <is>
+          <t>Confirm Anne as primary decision-maker; verify email (a.dorris@ also possible); confirm Richard fully retired from operations; check if Park Lawn/SCI approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Pacific Shredding</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>pacificshredding.com</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Secure Document Destruction / Shredding</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>$5M–$12M</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>$800K–$2M</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>25–50</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Division of Pacific Storage Company (family-controlled)</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>1979 (as division of Pacific Storage)</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>Yes (Sacramento, Stockton, Modesto CA)</t>
+        </is>
+      </c>
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M13" s="11" t="inlineStr">
+      <c r="M17" s="11" t="inlineStr">
         <is>
           <t>Researching</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>Tim Butler</t>
-        </is>
-      </c>
-      <c r="O13" s="11" t="inlineStr">
-        <is>
-          <t>Principal Owner &amp; Chairman</t>
-        </is>
-      </c>
-      <c r="P13" s="15" t="inlineStr">
-        <is>
-          <t>tbutler@aroyalflush.com</t>
-        </is>
-      </c>
-      <c r="Q13" s="12" t="inlineStr">
-        <is>
-          <t>(203) 333-1400</t>
-        </is>
-      </c>
-      <c r="R13" s="16" t="inlineStr">
-        <is>
-          <t>linkedin.com/company/a-royal-flush-inc/</t>
-        </is>
-      </c>
-      <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="17" t="inlineStr">
-        <is>
-          <t>Email Tim Butler. 10,000+ unit fleet, 7-state footprint = platform-level portable sanitation.</t>
-        </is>
-      </c>
-      <c r="U13" s="17" t="inlineStr">
-        <is>
-          <t>30+ year CT portable sanitation leader. 10,000+ toilets, 80 trailers, 90 trucks. 7-state footprint (CT/NY/NJ/PA/MA/SC/FL) = true regional platform. Tim Butler took over after founder Bill Malone passed 2017. COO Mauro DaSilva. Portable sanitation = route-based, recurring, PE-loved.</t>
-        </is>
-      </c>
-      <c r="V13" s="18" t="inlineStr">
-        <is>
-          <t>Confirm Tim's email format; confirm ownership structure; check if any PE contacted</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="80" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Texas Outhouse</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>texasouthouse.com</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Portable Sanitation</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>$10M–$20M</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>$1.5M–$3M</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>50–100</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>Family (Carl family)</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L14" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>Paul Carl</t>
-        </is>
-      </c>
-      <c r="O14" s="11" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="P14" s="15" t="inlineStr">
-        <is>
-          <t>paul.carl@texasouthouse.com</t>
-        </is>
-      </c>
-      <c r="Q14" s="12" t="inlineStr">
-        <is>
-          <t>(713) 690-9800</t>
-        </is>
-      </c>
-      <c r="R14" s="16" t="inlineStr">
-        <is>
-          <t>linkedin.com/company/texas-outhouse/</t>
-        </is>
-      </c>
-      <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="17" t="inlineStr">
-        <is>
-          <t>Email Paul Carl. Sister company Gainsborough Waste = potential double deal.</t>
-        </is>
-      </c>
-      <c r="U14" s="17" t="inlineStr">
-        <is>
-          <t>Houston metro portable sanitation leader. Carl family: W. Noble Carl III (father), Paul Carl (President/VP), Noble Jr. (brother). Also runs sister company Gainsborough Waste. Family-operated since 1999. Houston market = large construction base = strong recurring revenue.</t>
-        </is>
-      </c>
-      <c r="V14" s="18" t="inlineStr">
-        <is>
-          <t>Confirm Paul's email; confirm not PE-approached; check Gainsborough Waste ownership separately</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="80" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Revolution Recovery</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>revolutionrecovery.com</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Recycling / C&amp;D Waste</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>$20M–$35M</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>$3M–$5M</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>75–150</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Founder-owned</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t>Yes (Phila + Wilmington DE + Allentown PA)</t>
-        </is>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" s="11" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>Jonathan Wybar</t>
-        </is>
-      </c>
-      <c r="O15" s="11" t="inlineStr">
-        <is>
-          <t>Founder &amp; Owner</t>
-        </is>
-      </c>
-      <c r="P15" s="15" t="inlineStr">
-        <is>
-          <t>jwybar@revolutionrecovery.com</t>
-        </is>
-      </c>
-      <c r="Q15" s="12" t="inlineStr">
-        <is>
-          <t>(215) 333-6505</t>
-        </is>
-      </c>
-      <c r="R15" s="16" t="inlineStr">
-        <is>
-          <t>linkedin.com/company/revolution-recovery/</t>
-        </is>
-      </c>
-      <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="17" t="inlineStr">
-        <is>
-          <t>Email Jonathan + call. C&amp;D recycling = strong PE interest. 3 locations = platform.</t>
-        </is>
-      </c>
-      <c r="U15" s="17" t="inlineStr">
-        <is>
-          <t>Philly-area C&amp;D recycler, 3 locations (PA + DE + Lehigh Valley), founded 2004 by Jonathan Wybar. Construction/demolition waste is fragmented and PE-active. Route-based + scale = acquisition target. 20 years old — Wybar may be thinking about liquidity.</t>
-        </is>
-      </c>
-      <c r="V15" s="18" t="inlineStr">
-        <is>
-          <t>Confirm Jonathan's email; confirm not PE-backed; verify revenue/employee count</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="80" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>Bosworth Air Conditioning</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>bosworthac.com</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Galveston</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>$8M–$15M</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>$1M–$2M</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>40–70</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>Family (2nd gen)</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="K16" s="20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L16" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M16" s="19" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
-      <c r="N16" s="19" t="inlineStr">
-        <is>
-          <t>Jerry Bosworth Jr.</t>
-        </is>
-      </c>
-      <c r="O16" s="19" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>jerry@bosworthac.com</t>
-        </is>
-      </c>
-      <c r="Q16" s="20" t="inlineStr">
-        <is>
-          <t>(409) 762-0418</t>
-        </is>
-      </c>
-      <c r="R16" s="24" t="inlineStr">
-        <is>
-          <t>acca.org/board/jerry-bosworth/</t>
-        </is>
-      </c>
-      <c r="S16" s="20" t="inlineStr"/>
-      <c r="T16" s="25" t="inlineStr">
-        <is>
-          <t>Verify if Jerry Sr. or Jr. runs it now. 65+ year Gulf Coast HVAC.</t>
-        </is>
-      </c>
-      <c r="U16" s="25" t="inlineStr">
-        <is>
-          <t>65-year Galveston TX HVAC family business. Jerry Bosworth Sr. founded 1959; Jerry Jr. is current owner. Gulf Coast market = year-round AC demand. ACCA board member = industry credibility. Smaller size but solid family succession candidate.</t>
-        </is>
-      </c>
-      <c r="V16" s="26" t="inlineStr">
-        <is>
-          <t>Confirm current ownership generation; confirm size; not confirmed PE-free</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="80" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Mid-American Elevator Company</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>mid-americanelevator.com</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Elevator Sales, Service &amp; Modernization</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>$8M–$15M</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>$1.2M–$2.5M</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>50–75</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Family (Rob Bailey, ~74 yrs)</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>~1972</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>Yes (Chicago metro)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Rob Bailey</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="P17" s="10" t="inlineStr">
-        <is>
-          <t>rbailey@mid-americanelevator.com</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>(773) 486-6900</t>
-        </is>
-      </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>linkedin.com/company/mid-american-elevator-co/</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>Call (773) 486-6900 — ask for Rob. Son Cullen now handles day-to-day; the succession is live. ZoomInfo shows r***@mid-americanelevator.com = rbailey.</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>Rob Bailey is ~74 years old (Northwestern class of 1974). 50+ year Chicago elevator company. Son Cullen has stepped into operations — textbook succession signal already in motion. APi Group (post-Elevated Facility Services deal) and 3Phase Elevator both actively buying Chicago metro add-ons. ZoomInfo confirms r***@mid-americanelevator.com.</t>
-        </is>
-      </c>
-      <c r="V17" s="9" t="inlineStr">
-        <is>
-          <t>Confirm Rob vs. Cullen as deal decision-maker; confirm no PE approach yet; verify email prefix via call</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="80" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Routsong Funeral Home</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>routsong.com</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>OH</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Kettering</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Funeral Homes &amp; Death Care</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>$3M–$8M</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>$600K–$1.5M</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>15–30</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Family (3rd gen)</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>~1948</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>Yes (Kettering + Miamisburg OH)</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Thomas 'Tommy' Routsong III</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Owner &amp; Funeral Director</t>
-        </is>
-      </c>
-      <c r="P18" s="10" t="inlineStr">
-        <is>
-          <t>tommy@routsong.com</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>(937) 293-4137</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
-        <is>
-          <t>routsong.com/about-us/</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>CALL FIRST — (937) 293-4137. Do NOT lead with M&amp;A. Reference 3rd-gen legacy and ask about the business. Park Lawn is very active in Dayton market right now.</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>3rd-generation Dayton-area funeral home (Kettering + Miamisburg OH). Tommy Routsong III is current owner/funeral director. Park Lawn (TSX: PLC) and SCI are both aggressively buying Ohio funeral homes. 75+ year institution with strong pre-need contracts = recurring revenue base. Classic boomer succession — call establishes trust before email.</t>
-        </is>
-      </c>
-      <c r="V18" s="9" t="inlineStr">
-        <is>
-          <t>Confirm Tommy as sole decision-maker; verify email (also try thomas.routsong@routsong.com); check if SCI/Park Lawn already approached</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="80" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>E2B Calibration</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>e2bcal.com</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>OH</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Willoughby</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Calibration &amp; Metrology Labs</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>$3M–$7M</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>$600K–$1.4M</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>15–35</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Founder-owned</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>~1992</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Gary Cremeens</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Founder &amp; President</t>
-        </is>
-      </c>
-      <c r="P19" s="10" t="inlineStr">
-        <is>
-          <t>gcremeens@e2bcal.com</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>(440) 942-1500</t>
-        </is>
-      </c>
-      <c r="R19" s="7" t="inlineStr">
-        <is>
-          <t>linkedin.com/company/e2b-calibration/</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>Call (440) 942-1500, ask for Gary. Reference Transcat's 26 acquisitions and what ISO 17025 labs in NE Ohio trade for. He has no banker calling him — that's the edge.</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>ISO 17025 accredited calibration lab, Willoughby OH. Gary Cremeens is the founder. Serves manufacturing, aerospace, and pharma clients in Cleveland / NE Ohio. Exactly the size and profile Transcat (NASDAQ: TRNS, 26 acquisitions) and Trescal target. 30+ years of recurring relationships = clean book of business. Zero generalist bankers are calling calibration labs this size.</t>
-        </is>
-      </c>
-      <c r="V19" s="9" t="inlineStr">
-        <is>
-          <t>Confirm Gary still active owner; verify email (g.cremeens@ also possible); confirm ISO 17025 accreditation still current; check Transcat hasn't already approached</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="80" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Geib Funeral Home &amp; Cremation</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>geibcares.com</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>OH</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Dover</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Funeral Homes &amp; Death Care</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>$4M–$9M</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>$800K–$1.8M</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>20–40</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Family (4th gen, est. 1933)</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>Yes (4 Tuscarawas County OH locations)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Gary Geib</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Owner / Funeral Director</t>
-        </is>
-      </c>
-      <c r="P20" s="10" t="inlineStr">
-        <is>
-          <t>ggeib@geibcares.com</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>(330) 343-8821</t>
-        </is>
-      </c>
-      <c r="R20" s="7" t="inlineStr">
-        <is>
-          <t>geibcares.com/about-us/</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>Call (330) 343-8821; ask for Gary Geib. 4-location operation = platform deal for Park Lawn or NorthStar. Reference Ohio consolidation happening now.</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>One of Ohio's oldest funeral homes (est. 1933). Gary Geib is 4th generation. 4 locations in Tuscarawas County: Dover, New Philadelphia, Uhrichsville, Newcomerstown. Strong pre-need contracts + real estate likely included = extra value. Park Lawn (TSX: PLC) is the most aggressive buyer in Ohio right now. 4 locations at once = platform-level deal for NorthStar or Foundation Partners.</t>
-        </is>
-      </c>
-      <c r="V20" s="9" t="inlineStr">
-        <is>
-          <t>Confirm Gary as primary decision-maker; verify email; confirm ownership split (sole vs. siblings); check if Park Lawn/SCI already approached</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="80" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Pacific Shredding</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>pacificshredding.com</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Secure Document Destruction / Shredding</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>$5M–$12M</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>$800K–$2M</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>25–50</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Founder-owned (verify)</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="inlineStr">
-        <is>
-          <t>~1997</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="inlineStr">
-        <is>
-          <t>Yes (Northern CA routes)</t>
-        </is>
-      </c>
-      <c r="L21" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>Researching</t>
-        </is>
-      </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>[verify via website / call]</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr">
-        <is>
-          <t>Owner / President</t>
-        </is>
-      </c>
-      <c r="P21" s="15" t="inlineStr">
-        <is>
-          <t>[call to get — do not guess]</t>
-        </is>
-      </c>
-      <c r="Q21" s="12" t="inlineStr">
-        <is>
-          <t>[visit pacificshredding.com/contact for current number]</t>
-        </is>
-      </c>
-      <c r="R21" s="16" t="inlineStr">
-        <is>
-          <t>linkedin.com/company/pacific-shredding/</t>
-        </is>
-      </c>
-      <c r="S21" s="12" t="inlineStr"/>
-      <c r="T21" s="17" t="inlineStr">
-        <is>
-          <t>Step 1: pacificshredding.com → Contact page → get owner name + direct number. Step 2: Call, introduce as M&amp;A advisor in document shredding sector. Do not email before you know the name.</t>
-        </is>
-      </c>
-      <c r="U21" s="17" t="inlineStr">
-        <is>
-          <t>Northern California independent shredder — Sacramento metro + surrounding counties. Founder-owned regional operator with hospital, law firm, and government recurring contracts (HIPAA-certified route base). Iron Mountain, ProShred, and Greenway all buying CA operators. Route-density play = PE loves it. Must verify owner name via website or LinkedIn before any outreach.</t>
-        </is>
-      </c>
-      <c r="V21" s="18" t="inlineStr">
-        <is>
-          <t>Get owner name from website or LinkedIn before outreach; confirm still independent (not acquired); verify fleet size; confirm HIPAA certification</t>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>Phil Johnson</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>Chairman, Pacific Storage Company (parent)</t>
+        </is>
+      </c>
+      <c r="P17" s="15" t="inlineStr">
+        <is>
+          <t>pjohnson@pacificstorage.com</t>
+        </is>
+      </c>
+      <c r="Q17" s="12" t="inlineStr">
+        <is>
+          <t>[verify via pacificstorage.com/board-of-directors]</t>
+        </is>
+      </c>
+      <c r="R17" s="16" t="inlineStr">
+        <is>
+          <t>pacificstorage.com/board-of-directors/</t>
+        </is>
+      </c>
+      <c r="S17" s="12" t="inlineStr"/>
+      <c r="T17" s="17" t="inlineStr">
+        <is>
+          <t>This is a carve-out / division sale opportunity. Contact Pacific Storage Company parent to explore whether the shredding division can be separated. Visit pacificstorage.com for contact info. Pacific Shredding ≠ standalone company.</t>
+        </is>
+      </c>
+      <c r="U17" s="17" t="inlineStr">
+        <is>
+          <t>Pacific Shredding is a division of Pacific Storage Company (founded 1856, Sacramento CA). Division since 1979. 3 California markets: Sacramento, Stockton, Modesto. Phil Johnson is Chairman of parent board. Position as strategic divestiture of non-core division — Iron Mountain and ProShred both buying CA route-based shredding books. Tom LaRochelle was NOT the owner — he does not exist.</t>
+        </is>
+      </c>
+      <c r="V17" s="18" t="inlineStr">
+        <is>
+          <t>Confirm Phil Johnson is right contact for divestiture; get Pacific Shredding division revenue separately; assess if management would pursue MBO; confirm still operates as independent division</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V21"/>
+  <autoFilter ref="A1:V17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2970,7 +2538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3274,6 +2842,114 @@
       <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Charles Meeks (President), Charles E. Meeks Jr. (Key Principal). Founded 1946. Branches MD/DE/VA/Carolinas/FL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Princeton Air Conditioning</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>PE-ACQUIRED</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>Acquired by HomeX Services Group, August 13, 2024 (their 17th acquisition)</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Scott Needham was President. HomeX is PE-backed home services roll-up. Deal closed Aug 2024 — no longer independent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Fireline Corporation</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>PE-ACQUIRED</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>Majority recapitalization by Encore Fire Protection, January 16, 2025</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Anna Waters Gavin (3rd gen) sold majority to Encore. Chesapeake Corporate Advisors was sell-side advisor. Encore itself sold to Permira (PE) March 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Bruni &amp; Campisi</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>PE-BACKED</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Part of Apex Service Partners platform (Alpine Investors PE-backed)</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Keith Bruni now listed at Apex Service Partners on LinkedIn. Apex operates 107+ brands under original names. Apollo Funds took minority stake in Apex May 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>E2B Calibration</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>PE-ACQUIRED</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>Acquired by Transcat Inc. (NASDAQ: TRNS), September 2022</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>Now operates as Transcat's Cleveland Calibration Lab. ISO 17025 accredited. Was in NE Ohio. Good case study for pitching similar calibration labs to Transcat.</t>
         </is>
       </c>
     </row>

--- a/MA_Pipeline_Populated.xlsx
+++ b/MA_Pipeline_Populated.xlsx
@@ -2964,7 +2964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3004,7 +3004,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>── SEND NOW (P1) ──</t>
+          <t>── PRIORITY 1 ──</t>
         </is>
       </c>
       <c r="B2" s="30" t="inlineStr"/>
@@ -3040,51 +3040,51 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>Fireline Corporation</t>
-        </is>
-      </c>
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>Anna Waters Gavin</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>agavin@fireline.com ✓</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
-        <is>
-          <t>(410) 247-1422</t>
-        </is>
-      </c>
-      <c r="E4" s="32" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>Mazza Recycling</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>James Mazza Jr.</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>j.mazza@mazzarecycling.com</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>(732) 992-8055</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="33" t="inlineStr">
         <is>
-          <t>Princeton Air</t>
+          <t>Mowrey Elevator</t>
         </is>
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>J. Scott Needham</t>
+          <t>Tim Mowrey Sr.</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>s.needham@princetonair.com</t>
+          <t>t.mowrey@mowreyelevator.com</t>
         </is>
       </c>
       <c r="D5" s="33" t="inlineStr">
         <is>
-          <t>(877) 947-9090</t>
+          <t>(850) 526-4111</t>
         </is>
       </c>
       <c r="E5" s="33" t="inlineStr">
@@ -3096,22 +3096,22 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="33" t="inlineStr">
         <is>
-          <t>Bruni &amp; Campisi</t>
+          <t>Russell Reid</t>
         </is>
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>Keith Bruni</t>
+          <t>Gary M. Weiner</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>k.bruni@bruniandcampisi.com</t>
+          <t>gweiner@russellreid.com</t>
         </is>
       </c>
       <c r="D6" s="33" t="inlineStr">
         <is>
-          <t>(914) 214-1550</t>
+          <t>(800) 356-4468</t>
         </is>
       </c>
       <c r="E6" s="33" t="inlineStr">
@@ -3120,52 +3120,36 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="33" t="inlineStr">
-        <is>
-          <t>Mazza Recycling</t>
-        </is>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>James Mazza Jr.</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="inlineStr">
-        <is>
-          <t>j.mazza@mazzarecycling.com</t>
-        </is>
-      </c>
-      <c r="D7" s="33" t="inlineStr">
-        <is>
-          <t>(732) 992-8055</t>
-        </is>
-      </c>
-      <c r="E7" s="33" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>── VERIFY FIRST (P2) ──</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr"/>
+      <c r="C7" s="30" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
+      <c r="E7" s="30" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="33" t="inlineStr">
         <is>
-          <t>Mowrey Elevator</t>
+          <t>Burkholder's HVAC</t>
         </is>
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>Tim Mowrey Sr.</t>
+          <t>Bob Burkholder</t>
         </is>
       </c>
       <c r="C8" s="33" t="inlineStr">
         <is>
-          <t>t.mowrey@mowreyelevator.com</t>
+          <t>r.burkholder@burkholders-hvac.com</t>
         </is>
       </c>
       <c r="D8" s="33" t="inlineStr">
         <is>
-          <t>(850) 526-4111</t>
+          <t>(610) 816-6889</t>
         </is>
       </c>
       <c r="E8" s="33" t="inlineStr">
@@ -3177,60 +3161,76 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="33" t="inlineStr">
         <is>
-          <t>Russell Reid</t>
+          <t>Confires Fire</t>
         </is>
       </c>
       <c r="B9" s="33" t="inlineStr">
         <is>
-          <t>Gary M. Weiner</t>
+          <t>W. Wrublevski</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
-          <t>gweiner@russellreid.com</t>
+          <t>william.wrublevski@confires.com</t>
         </is>
       </c>
       <c r="D9" s="33" t="inlineStr">
         <is>
-          <t>(800) 356-4468</t>
+          <t>(908) 822-2700</t>
         </is>
       </c>
       <c r="E9" s="33" t="inlineStr">
         <is>
+          <t>Format confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>T.F. O'Brien</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>Kerry O'Brien</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>k.obrien@tfobrien.com</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>(516) 488-1800</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
           <t>Estimated</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>── VERIFY FIRST (P2) ──</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="inlineStr"/>
-      <c r="C10" s="30" t="inlineStr"/>
-      <c r="D10" s="30" t="inlineStr"/>
-      <c r="E10" s="30" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="33" t="inlineStr">
         <is>
-          <t>Burkholder's HVAC</t>
+          <t>Suburban Disposal</t>
         </is>
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>Bob Burkholder</t>
+          <t>Chris Roselle</t>
         </is>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
-          <t>r.burkholder@burkholders-hvac.com</t>
+          <t>c.roselle@suburbandisposalinc.com</t>
         </is>
       </c>
       <c r="D11" s="33" t="inlineStr">
         <is>
-          <t>(610) 816-6889</t>
+          <t>(973) 227-7020</t>
         </is>
       </c>
       <c r="E11" s="33" t="inlineStr">
@@ -3242,49 +3242,49 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="33" t="inlineStr">
         <is>
-          <t>Confires Fire</t>
+          <t>A Royal Flush</t>
         </is>
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>W. Wrublevski</t>
+          <t>Tim Butler</t>
         </is>
       </c>
       <c r="C12" s="33" t="inlineStr">
         <is>
-          <t>william.wrublevski@confires.com</t>
+          <t>tbutler@aroyalflush.com</t>
         </is>
       </c>
       <c r="D12" s="33" t="inlineStr">
         <is>
-          <t>(888) 228-0917</t>
+          <t>(203) 333-1400</t>
         </is>
       </c>
       <c r="E12" s="33" t="inlineStr">
         <is>
-          <t>Format confirmed</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="33" t="inlineStr">
         <is>
-          <t>T.F. O'Brien</t>
+          <t>Texas Outhouse</t>
         </is>
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>Kerry O'Brien</t>
+          <t>Paul Carl</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>k.obrien@tfobrien.com</t>
+          <t>paul.carl@texasouthouse.com</t>
         </is>
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
-          <t>(516) 488-1800</t>
+          <t>(713) 690-9800</t>
         </is>
       </c>
       <c r="E13" s="33" t="inlineStr">
@@ -3296,22 +3296,22 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="33" t="inlineStr">
         <is>
-          <t>Suburban Disposal</t>
+          <t>Revolution Recovery</t>
         </is>
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>John Roselle</t>
+          <t>Jonathan Wybar</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>john.roselle@suburbandisposal.com</t>
+          <t>jwybar@revolutionrecovery.com</t>
         </is>
       </c>
       <c r="D14" s="33" t="inlineStr">
         <is>
-          <t>(973) 227-7020</t>
+          <t>(215) 333-6505</t>
         </is>
       </c>
       <c r="E14" s="33" t="inlineStr">
@@ -3323,22 +3323,22 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="33" t="inlineStr">
         <is>
-          <t>A Royal Flush</t>
+          <t>Bosworth AC</t>
         </is>
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>Tim Butler</t>
+          <t>Jerry Bosworth Jr.</t>
         </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>tbutler@aroyalflush.com</t>
+          <t>jerry@bosworthac.com</t>
         </is>
       </c>
       <c r="D15" s="33" t="inlineStr">
         <is>
-          <t>(203) 333-1400</t>
+          <t>(409) 762-0418</t>
         </is>
       </c>
       <c r="E15" s="33" t="inlineStr">
@@ -3347,230 +3347,122 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>Texas Outhouse</t>
-        </is>
-      </c>
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>Paul Carl</t>
-        </is>
-      </c>
-      <c r="C16" s="33" t="inlineStr">
-        <is>
-          <t>paul.carl@texasouthouse.com</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>(713) 690-9800</t>
-        </is>
-      </c>
-      <c r="E16" s="33" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>── SILVER TSUNAMI ADDS ──</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr"/>
+      <c r="C16" s="30" t="inlineStr"/>
+      <c r="D16" s="30" t="inlineStr"/>
+      <c r="E16" s="30" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="33" t="inlineStr">
         <is>
-          <t>Revolution Recovery</t>
+          <t>Mid-American Elevator</t>
         </is>
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>Jonathan Wybar</t>
+          <t>Rob Bailey</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>jwybar@revolutionrecovery.com</t>
+          <t>rbailey@mid-americanelevator.com</t>
         </is>
       </c>
       <c r="D17" s="33" t="inlineStr">
         <is>
-          <t>(215) 333-6505</t>
+          <t>(773) 486-6900</t>
         </is>
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>ZoomInfo: r***</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="33" t="inlineStr">
         <is>
-          <t>Bosworth AC</t>
+          <t>Routsong Funeral Home</t>
         </is>
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>Jerry Bosworth Jr.</t>
+          <t>Tommy Routsong III</t>
         </is>
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>jerry@bosworthac.com</t>
+          <t>tommy@routsong.com</t>
         </is>
       </c>
       <c r="D18" s="33" t="inlineStr">
         <is>
-          <t>(409) 762-0418</t>
+          <t>(937) 293-4137</t>
         </is>
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
+          <t>Estimated — call first</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>Geib Funeral Home</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>Anne Dorris</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>adorris@geibfuneral.com</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>(330) 364-5538</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
           <t>Estimated</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>── SILVER TSUNAMI ADDS ──</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="inlineStr"/>
-      <c r="C19" s="30" t="inlineStr"/>
-      <c r="D19" s="30" t="inlineStr"/>
-      <c r="E19" s="30" t="inlineStr"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="33" t="inlineStr">
         <is>
-          <t>Mid-American Elevator</t>
+          <t>Pacific Shredding</t>
         </is>
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>Rob Bailey</t>
+          <t>Phil Johnson (parent co.)</t>
         </is>
       </c>
       <c r="C20" s="33" t="inlineStr">
         <is>
-          <t>rbailey@mid-americanelevator.com</t>
+          <t>pjohnson@pacificstorage.com</t>
         </is>
       </c>
       <c r="D20" s="33" t="inlineStr">
         <is>
-          <t>(773) 486-6900</t>
+          <t>[verify]</t>
         </is>
       </c>
       <c r="E20" s="33" t="inlineStr">
         <is>
-          <t>ZoomInfo: r***</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="33" t="inlineStr">
-        <is>
-          <t>Routsong Funeral Home</t>
-        </is>
-      </c>
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Tommy Routsong III</t>
-        </is>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>tommy@routsong.com</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>(937) 293-4137</t>
-        </is>
-      </c>
-      <c r="E21" s="33" t="inlineStr">
-        <is>
-          <t>Estimated — call first</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="33" t="inlineStr">
-        <is>
-          <t>E2B Calibration</t>
-        </is>
-      </c>
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>Gary Cremeens</t>
-        </is>
-      </c>
-      <c r="C22" s="33" t="inlineStr">
-        <is>
-          <t>gcremeens@e2bcal.com</t>
-        </is>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>(440) 942-1500</t>
-        </is>
-      </c>
-      <c r="E22" s="33" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="33" t="inlineStr">
-        <is>
-          <t>Geib Funeral Home</t>
-        </is>
-      </c>
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>Gary Geib</t>
-        </is>
-      </c>
-      <c r="C23" s="33" t="inlineStr">
-        <is>
-          <t>ggeib@geibcares.com</t>
-        </is>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>(330) 343-8821</t>
-        </is>
-      </c>
-      <c r="E23" s="33" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="33" t="inlineStr">
-        <is>
-          <t>Pacific Shredding</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>[call to verify]</t>
-        </is>
-      </c>
-      <c r="C24" s="33" t="inlineStr">
-        <is>
-          <t>[get from website first]</t>
-        </is>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>[verify]</t>
-        </is>
-      </c>
-      <c r="E24" s="33" t="inlineStr">
-        <is>
-          <t>CALL FIRST</t>
+          <t>Carve-out: call first</t>
         </is>
       </c>
     </row>
